--- a/data/trans_dic/IP18A01-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP18A01-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación</t>
+          <t>Menores que su última consulta al médico fue por vacunación (tasa de respuesta: 98,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,37 +717,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,39; 26,59</t>
+          <t>14,01; 26,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,52; 30,99</t>
+          <t>19,8; 32,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,53; 29,26</t>
+          <t>17,94; 29,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,11; 31,99</t>
+          <t>5,11; 32,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,06; 26,33</t>
+          <t>14,12; 26,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,95; 32,49</t>
+          <t>19,1; 31,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,55; 28,04</t>
+          <t>15,65; 27,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,86; 24,63</t>
+          <t>15,41; 24,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,69; 30,08</t>
+          <t>21,48; 29,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,24; 26,53</t>
+          <t>18,88; 27,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,98; 24,59</t>
+          <t>7,39; 24,85</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,53; 9,92</t>
+          <t>4,39; 9,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 11,27</t>
+          <t>4,69; 11,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 9,64</t>
+          <t>3,94; 9,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,66</t>
+          <t>0,0; 13,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,58; 11,21</t>
+          <t>5,38; 11,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,39; 12,5</t>
+          <t>6,31; 12,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 11,84</t>
+          <t>5,48; 11,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 12,51</t>
+          <t>1,08; 12,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,64; 9,5</t>
+          <t>5,8; 9,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,56; 10,77</t>
+          <t>6,5; 10,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,53; 9,61</t>
+          <t>5,6; 9,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 9,18</t>
+          <t>0,97; 9,37</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 9,81</t>
+          <t>2,37; 9,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 8,98</t>
+          <t>2,64; 8,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 7,02</t>
+          <t>1,95; 7,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 18,58</t>
+          <t>1,27; 18,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 8,42</t>
+          <t>2,34; 8,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,73</t>
+          <t>1,17; 6,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 7,77</t>
+          <t>2,21; 7,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,72</t>
+          <t>3,02; 7,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,79</t>
+          <t>2,21; 6,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,74; 6,4</t>
+          <t>2,61; 6,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 8,56</t>
+          <t>0,56; 7,81</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 9,69</t>
+          <t>3,35; 9,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 6,24</t>
+          <t>1,09; 6,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 11,98</t>
+          <t>4,93; 12,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,16</t>
+          <t>0,0; 21,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 7,16</t>
+          <t>2,04; 7,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,64</t>
+          <t>2,35; 7,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 7,78</t>
+          <t>1,72; 7,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,12</t>
+          <t>0,0; 12,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 7,12</t>
+          <t>3,31; 7,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,96</t>
+          <t>2,24; 5,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,77</t>
+          <t>3,81; 8,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 10,81</t>
+          <t>1,33; 12,61</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,81; 10,52</t>
+          <t>6,86; 10,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,98; 11,86</t>
+          <t>7,97; 11,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,76; 11,4</t>
+          <t>7,51; 11,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 12,66</t>
+          <t>3,62; 12,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,59; 10,17</t>
+          <t>6,64; 10,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,26; 12,31</t>
+          <t>8,19; 11,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,86; 10,76</t>
+          <t>7,07; 10,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 7,47</t>
+          <t>1,93; 7,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,2; 9,94</t>
+          <t>7,18; 9,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,61; 11,22</t>
+          <t>8,65; 11,42</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,91; 10,46</t>
+          <t>7,84; 10,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,11</t>
+          <t>3,53; 8,14</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su última consulta al médico fue por vacunación (tasa de respuesta: 98,73%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>20099</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>35939</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>29573</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2748</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>21144</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>36211</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>25559</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>41242</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>72150</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>55132</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5049</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>14255; 27172</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28027; 45351</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>22785; 37650</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>833; 5322</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>15202; 28485</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>27050; 45129</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>18443; 32915</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>784; 5113</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>32269; 50587</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>60821; 84527</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>46215; 66892</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2568; 8633</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>16080</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16939</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11805</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>18571</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>22816</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>19733</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1541</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>34651</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>39755</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>31538</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2304</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>10166; 22752</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>10313; 24395</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>7562; 18645</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3841</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>12553; 25850</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>15951; 31754</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>12940; 27499</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>365; 4181</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>26964; 44602</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>30707; 49880</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>23977; 41813</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>603; 5801</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>5615</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>7845</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6967</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1948</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5499</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4594</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>7356</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>11114</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12439</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>14323</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1948</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2508; 10289</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3966; 13385</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3302; 12009</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>397; 5726</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2708; 10301</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1744; 9981</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3733; 13251</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>6704; 17550</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6628; 19407</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>8829; 21539</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>381; 5321</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>9333</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4386</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11902</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6972</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7198</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5974</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1501</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>11584</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>17876</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>5314; 15615</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1653; 9327</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>7486; 18837</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5214</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3409; 12217</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>3853; 12774</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2525; 11451</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5250</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>10775; 23685</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>7077; 18159</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>11379; 25862</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>891; 8457</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>51127</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>65108</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>60248</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>52186</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>70819</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>58621</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5343</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>103313</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>135927</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>118869</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>12503</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>41000; 62606</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>52879; 77802</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>48061; 73365</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>3635; 12644</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>41419; 64291</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>57925; 84753</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>47364; 70654</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2536; 9440</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>87795; 118659</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>118617; 156587</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>102744; 138204</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>8178; 18872</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP18A01-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP18A01-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,01; 26,71</t>
+          <t>14,33; 26,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,8; 32,03</t>
+          <t>19,98; 32,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,94; 29,64</t>
+          <t>18,34; 30,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,11; 32,66</t>
+          <t>6,87; 33,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,12; 26,45</t>
+          <t>14,07; 26,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,1; 31,87</t>
+          <t>19,9; 32,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,65; 27,94</t>
+          <t>16,34; 28,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 27,72</t>
+          <t>4,34; 28,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,41; 24,16</t>
+          <t>15,84; 24,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,48; 29,85</t>
+          <t>21,29; 30,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,88; 27,32</t>
+          <t>18,27; 27,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,39; 24,85</t>
+          <t>6,97; 23,91</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 9,82</t>
+          <t>4,49; 9,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,69; 11,1</t>
+          <t>5,02; 11,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,94; 9,71</t>
+          <t>4,0; 9,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,62</t>
+          <t>0,0; 13,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 11,08</t>
+          <t>5,34; 11,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,31; 12,57</t>
+          <t>5,98; 12,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,48; 11,64</t>
+          <t>5,42; 11,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 12,4</t>
+          <t>1,14; 12,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,8; 9,59</t>
+          <t>5,75; 9,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,5; 10,56</t>
+          <t>6,59; 10,82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,6; 9,76</t>
+          <t>5,38; 9,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 9,37</t>
+          <t>0,95; 8,98</t>
         </is>
       </c>
     </row>
@@ -997,37 +997,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 9,7</t>
+          <t>2,47; 10,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 8,91</t>
+          <t>2,49; 9,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,09</t>
+          <t>2,24; 7,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 18,3</t>
+          <t>1,28; 19,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 8,91</t>
+          <t>2,35; 9,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,67</t>
+          <t>1,3; 6,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 7,85</t>
+          <t>2,18; 7,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,92</t>
+          <t>2,84; 7,83</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 6,47</t>
+          <t>2,57; 6,66</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,37</t>
+          <t>2,66; 6,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 7,81</t>
+          <t>0,56; 8,09</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 9,84</t>
+          <t>3,33; 9,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 6,13</t>
+          <t>1,05; 5,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,93; 12,41</t>
+          <t>4,71; 12,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,26</t>
+          <t>0,0; 20,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 7,3</t>
+          <t>2,17; 7,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 7,8</t>
+          <t>2,31; 7,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 7,8</t>
+          <t>1,96; 7,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,34</t>
+          <t>0,0; 12,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,31; 7,27</t>
+          <t>3,17; 7,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 5,75</t>
+          <t>2,05; 5,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 8,66</t>
+          <t>3,89; 8,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 12,61</t>
+          <t>1,17; 10,78</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,86; 10,47</t>
+          <t>7,05; 10,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,97; 11,72</t>
+          <t>8,12; 11,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,51; 11,46</t>
+          <t>7,65; 11,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,62; 12,6</t>
+          <t>3,76; 12,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,64; 10,3</t>
+          <t>6,67; 10,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,19; 11,98</t>
+          <t>8,25; 12,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,07; 10,55</t>
+          <t>7,16; 10,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 7,17</t>
+          <t>1,92; 7,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,18; 9,71</t>
+          <t>7,27; 9,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,65; 11,42</t>
+          <t>8,68; 11,36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,84; 10,55</t>
+          <t>7,84; 10,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 8,14</t>
+          <t>3,33; 8,02</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14255; 27172</t>
+          <t>14579; 26874</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28027; 45351</t>
+          <t>28293; 45307</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22785; 37650</t>
+          <t>23288; 38193</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>833; 5322</t>
+          <t>1120; 5517</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15202; 28485</t>
+          <t>15155; 28387</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27050; 45129</t>
+          <t>28180; 45747</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18443; 32915</t>
+          <t>19251; 33694</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>784; 5113</t>
+          <t>800; 5228</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32269; 50587</t>
+          <t>33177; 51808</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>60821; 84527</t>
+          <t>60286; 85486</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46215; 66892</t>
+          <t>44721; 66436</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2568; 8633</t>
+          <t>2420; 8307</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10166; 22752</t>
+          <t>10401; 22575</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10313; 24395</t>
+          <t>11030; 24224</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7562; 18645</t>
+          <t>7677; 18261</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3841</t>
+          <t>0; 3819</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12553; 25850</t>
+          <t>12454; 25933</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15951; 31754</t>
+          <t>15119; 31177</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12940; 27499</t>
+          <t>12803; 26795</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>365; 4181</t>
+          <t>385; 4122</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26964; 44602</t>
+          <t>26753; 45503</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30707; 49880</t>
+          <t>31161; 51110</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23977; 41813</t>
+          <t>23032; 40803</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>603; 5801</t>
+          <t>588; 5559</t>
         </is>
       </c>
     </row>
@@ -2061,37 +2061,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2508; 10289</t>
+          <t>2615; 10867</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3966; 13385</t>
+          <t>3737; 13591</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3302; 12009</t>
+          <t>3795; 12113</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>397; 5726</t>
+          <t>402; 6003</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2708; 10301</t>
+          <t>2716; 10605</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1744; 9981</t>
+          <t>1949; 10429</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3733; 13251</t>
+          <t>3675; 12522</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6704; 17550</t>
+          <t>6294; 17351</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6628; 19407</t>
+          <t>7705; 19980</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8829; 21539</t>
+          <t>9004; 21690</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>381; 5321</t>
+          <t>380; 5513</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5314; 15615</t>
+          <t>5284; 15716</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1653; 9327</t>
+          <t>1603; 9073</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7486; 18837</t>
+          <t>7148; 18405</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5214</t>
+          <t>0; 5021</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3409; 12217</t>
+          <t>3629; 12521</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3853; 12774</t>
+          <t>3776; 12776</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2525; 11451</t>
+          <t>2881; 11070</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 5250</t>
+          <t>0; 5312</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10775; 23685</t>
+          <t>10346; 23999</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7077; 18159</t>
+          <t>6480; 17201</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11379; 25862</t>
+          <t>11613; 26015</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>891; 8457</t>
+          <t>787; 7232</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>41000; 62606</t>
+          <t>42169; 63698</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>52879; 77802</t>
+          <t>53923; 77796</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48061; 73365</t>
+          <t>49014; 74082</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3635; 12644</t>
+          <t>3769; 12784</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>41419; 64291</t>
+          <t>41648; 64459</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57925; 84753</t>
+          <t>58366; 85503</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47364; 70654</t>
+          <t>47953; 72760</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2536; 9440</t>
+          <t>2529; 10005</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>87795; 118659</t>
+          <t>88837; 120141</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>118617; 156587</t>
+          <t>119009; 155819</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>102744; 138204</t>
+          <t>102758; 135141</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8178; 18872</t>
+          <t>7716; 18602</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP18A01-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP18A01-Edad-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación (tasa de respuesta: 98,73%)</t>
+          <t>Menores cuya última consulta médica fue por vacunación (tasa de respuesta: 98,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19,64%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25,57%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21,69%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11,73%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>19,76%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>25,39%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>23,28%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16,86%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>19,64%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>25,57%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>21,69%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,33; 26,42</t>
+          <t>14,06; 26,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,98; 32,0</t>
+          <t>19,95; 32,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,34; 30,07</t>
+          <t>15,55; 28,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,87; 33,85</t>
+          <t>3,87; 26,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,07; 26,36</t>
+          <t>14,39; 26,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,9; 32,31</t>
+          <t>19,52; 30,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,34; 28,6</t>
+          <t>17,53; 29,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,34; 28,34</t>
+          <t>5,71; 30,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,84; 24,74</t>
+          <t>15,86; 24,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21,29; 30,19</t>
+          <t>21,69; 30,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,27; 27,14</t>
+          <t>18,24; 26,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,97; 23,91</t>
+          <t>6,42; 23,41</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,03%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8,35%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4,2%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>6,94%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>7,7%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>6,15%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,03%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 9,75</t>
+          <t>5,58; 11,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,02; 11,02</t>
+          <t>6,39; 12,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 9,51</t>
+          <t>5,87; 11,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,54</t>
+          <t>0,99; 11,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,34; 11,11</t>
+          <t>4,53; 9,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,98; 12,34</t>
+          <t>5,25; 11,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,42; 11,34</t>
+          <t>4,0; 9,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 12,22</t>
+          <t>0,0; 14,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,75; 9,79</t>
+          <t>5,64; 9,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,59; 10,82</t>
+          <t>6,56; 10,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 9,53</t>
+          <t>5,53; 9,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,98</t>
+          <t>0,88; 9,08</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5,3%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5,22%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4,11%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,75%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 10,25</t>
+          <t>2,35; 8,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 9,05</t>
+          <t>1,3; 6,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,15</t>
+          <t>2,19; 7,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 19,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 9,17</t>
+          <t>2,49; 9,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,97</t>
+          <t>2,37; 8,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 7,42</t>
+          <t>2,14; 7,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,16; 19,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 7,83</t>
+          <t>3,02; 7,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,66</t>
+          <t>2,35; 6,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 6,41</t>
+          <t>2,74; 6,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 8,09</t>
+          <t>0,53; 9,08</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,07%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5,88%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,88%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7,84%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 9,9</t>
+          <t>2,09; 7,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,96</t>
+          <t>2,3; 7,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 12,13</t>
+          <t>2,04; 7,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,47</t>
+          <t>0,0; 13,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,49</t>
+          <t>3,35; 9,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 7,8</t>
+          <t>1,26; 6,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,54</t>
+          <t>4,53; 11,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,49</t>
+          <t>0,0; 21,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,36</t>
+          <t>3,19; 7,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,45</t>
+          <t>2,05; 5,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 8,71</t>
+          <t>3,95; 8,77</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,78</t>
+          <t>1,41; 11,47</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8,36%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8,75%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>8,55%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>9,81%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>9,41%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8,36%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,05; 10,65</t>
+          <t>6,59; 10,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,12; 11,72</t>
+          <t>8,26; 12,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,65; 11,57</t>
+          <t>6,86; 10,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 12,74</t>
+          <t>1,87; 7,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,67; 10,33</t>
+          <t>6,81; 10,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,25; 12,08</t>
+          <t>7,98; 11,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,16; 10,86</t>
+          <t>7,76; 11,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,6</t>
+          <t>3,45; 12,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,27; 9,83</t>
+          <t>7,2; 9,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,68; 11,36</t>
+          <t>8,61; 11,22</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,84; 10,32</t>
+          <t>7,91; 10,46</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,33; 8,02</t>
+          <t>3,35; 8,23</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación (tasa de respuesta: 98,73%)</t>
+          <t>Menores cuya última consulta médica fue por vacunación (tasa de respuesta: 98,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21144</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>36211</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25559</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1801</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>20099</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>35939</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>29573</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2748</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>21144</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>36211</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>25559</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>4133</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14579; 26874</t>
+          <t>15135; 28351</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28293; 45307</t>
+          <t>28248; 46010</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23288; 38193</t>
+          <t>18319; 33038</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1120; 5517</t>
+          <t>594; 4077</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15155; 28387</t>
+          <t>14633; 27041</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28180; 45747</t>
+          <t>27637; 43873</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19251; 33694</t>
+          <t>22263; 37165</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>800; 5228</t>
+          <t>861; 4615</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33177; 51808</t>
+          <t>33200; 51567</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>60286; 85486</t>
+          <t>61426; 85173</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44721; 66436</t>
+          <t>44665; 64952</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2420; 8307</t>
+          <t>1952; 7123</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>18571</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>22816</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19733</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>16080</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>16939</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11805</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>763</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18571</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>22816</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19733</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>734</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>1959</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10401; 22575</t>
+          <t>13030; 26160</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11030; 24224</t>
+          <t>16141; 31575</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7677; 18261</t>
+          <t>13875; 27971</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3819</t>
+          <t>289; 3401</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12454; 25933</t>
+          <t>10495; 22980</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15119; 31177</t>
+          <t>11549; 24783</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12803; 26795</t>
+          <t>7677; 18511</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>385; 4122</t>
+          <t>0; 3677</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26753; 45503</t>
+          <t>26226; 44154</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31161; 51110</t>
+          <t>30975; 50872</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23032; 40803</t>
+          <t>23685; 41146</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>588; 5559</t>
+          <t>479; 4951</t>
         </is>
       </c>
     </row>
@@ -1930,37 +1930,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>5499</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4594</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7356</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>5615</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>7845</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>6967</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1948</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5499</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4594</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>7356</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1982</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2615; 10867</t>
+          <t>2721; 9741</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3737; 13591</t>
+          <t>1947; 10077</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3795; 12113</t>
+          <t>3690; 13107</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>402; 6003</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2716; 10605</t>
+          <t>2642; 10404</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1949; 10429</t>
+          <t>3557; 13486</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3675; 12522</t>
+          <t>3621; 11892</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>343; 5697</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6294; 17351</t>
+          <t>6704; 17105</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7705; 19980</t>
+          <t>7056; 20373</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9004; 21690</t>
+          <t>9266; 21638</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>380; 5513</t>
+          <t>346; 5915</t>
         </is>
       </c>
     </row>
@@ -2133,37 +2133,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6972</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7198</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5974</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1522</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>9333</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4386</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>11902</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6972</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7198</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5974</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3313</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5284; 15716</t>
+          <t>3499; 11976</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1603; 9073</t>
+          <t>3760; 12515</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7148; 18405</t>
+          <t>3003; 11421</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5021</t>
+          <t>0; 5416</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3629; 12521</t>
+          <t>5308; 15375</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3776; 12776</t>
+          <t>1921; 9490</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2881; 11070</t>
+          <t>6878; 18181</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 5312</t>
+          <t>0; 5517</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10346; 23999</t>
+          <t>10392; 23209</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6480; 17201</t>
+          <t>6465; 18836</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11613; 26015</t>
+          <t>11798; 26201</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>787; 7232</t>
+          <t>946; 7703</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>52186</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>70819</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>58621</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4549</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>51127</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>65108</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>60248</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>7160</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>52186</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>70819</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>58621</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>11387</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>42169; 63698</t>
+          <t>41097; 63437</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>53923; 77796</t>
+          <t>58462; 87104</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49014; 74082</t>
+          <t>45971; 72075</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3769; 12784</t>
+          <t>2282; 8806</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>41648; 64459</t>
+          <t>40701; 62933</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58366; 85503</t>
+          <t>52968; 78747</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47953; 72760</t>
+          <t>49663; 72997</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2529; 10005</t>
+          <t>3298; 12315</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>88837; 120141</t>
+          <t>87981; 121498</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>119009; 155819</t>
+          <t>118088; 153873</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>102758; 135141</t>
+          <t>103583; 137035</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7716; 18602</t>
+          <t>7286; 17885</t>
         </is>
       </c>
     </row>
